--- a/Results/TestCases/XLSX/myinfo_TestCases.xlsx
+++ b/Results/TestCases/XLSX/myinfo_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="70">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -72,7 +72,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>SKIPPED</t>
+    <t>PASSED</t>
   </si>
   <si>
     <t>TC_MYINFO_02</t>
@@ -81,6 +81,9 @@
     <t>Upload profile image</t>
   </si>
   <si>
+    <t>FAILED</t>
+  </si>
+  <si>
     <t>TC_MYINFO_03</t>
   </si>
   <si>
@@ -177,7 +180,7 @@
     <t>TC_MYINFO_18</t>
   </si>
   <si>
-    <t>Verify Driver\</t>
+    <t>Verify Driver's License Number field is visible</t>
   </si>
   <si>
     <t>TC_MYINFO_19</t>
@@ -226,7 +229,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -246,12 +249,18 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF5A6268"/>
+      <color rgb="FF107C41"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFA51D24"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -265,7 +274,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E3E5"/>
+        <fgColor rgb="FFD1E7DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -307,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -316,6 +330,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -771,13 +788,13 @@
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>19</v>
+      <c r="K3" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -786,13 +803,13 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -812,7 +829,7 @@
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -821,13 +838,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -839,7 +856,7 @@
         <v>17</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>19</v>
@@ -847,7 +864,7 @@
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -856,13 +873,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -874,7 +891,7 @@
         <v>17</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>19</v>
@@ -882,7 +899,7 @@
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -891,13 +908,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -909,7 +926,7 @@
         <v>17</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>19</v>
@@ -917,7 +934,7 @@
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -926,13 +943,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -944,7 +961,7 @@
         <v>17</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>19</v>
@@ -952,7 +969,7 @@
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -961,13 +978,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -979,7 +996,7 @@
         <v>17</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>19</v>
@@ -987,7 +1004,7 @@
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -996,13 +1013,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -1014,7 +1031,7 @@
         <v>17</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>19</v>
@@ -1022,7 +1039,7 @@
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1031,13 +1048,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -1049,7 +1066,7 @@
         <v>17</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>19</v>
@@ -1057,7 +1074,7 @@
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1066,13 +1083,13 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -1084,15 +1101,15 @@
         <v>17</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1101,13 +1118,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1119,7 +1136,7 @@
         <v>17</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>19</v>
@@ -1127,7 +1144,7 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1136,13 +1153,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -1154,7 +1171,7 @@
         <v>17</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>19</v>
@@ -1162,7 +1179,7 @@
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1171,13 +1188,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1189,7 +1206,7 @@
         <v>17</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>19</v>
@@ -1197,7 +1214,7 @@
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1206,13 +1223,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -1224,7 +1241,7 @@
         <v>17</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>19</v>
@@ -1232,7 +1249,7 @@
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1241,13 +1258,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -1259,7 +1276,7 @@
         <v>17</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>19</v>
@@ -1267,7 +1284,7 @@
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1276,13 +1293,13 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -1294,7 +1311,7 @@
         <v>17</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>19</v>
@@ -1302,7 +1319,7 @@
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1311,13 +1328,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -1329,15 +1346,15 @@
         <v>17</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1346,13 +1363,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -1364,7 +1381,7 @@
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>19</v>
@@ -1372,7 +1389,7 @@
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1381,13 +1398,13 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1399,7 +1416,7 @@
         <v>17</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>19</v>
@@ -1407,7 +1424,7 @@
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1416,13 +1433,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1434,7 +1451,7 @@
         <v>17</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>19</v>
@@ -1442,7 +1459,7 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1451,13 +1468,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1469,7 +1486,7 @@
         <v>17</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>19</v>
@@ -1477,7 +1494,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1486,13 +1503,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1504,7 +1521,7 @@
         <v>17</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>19</v>
@@ -1512,7 +1529,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1521,13 +1538,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1539,7 +1556,7 @@
         <v>17</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>19</v>
@@ -1547,7 +1564,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1556,13 +1573,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1574,7 +1591,7 @@
         <v>17</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>19</v>

--- a/Results/TestCases/XLSX/myinfo_TestCases.xlsx
+++ b/Results/TestCases/XLSX/myinfo_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="107">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -58,15 +58,16 @@
     <t>Positive</t>
   </si>
   <si>
-    <t>OrangeHRM application is accessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to page
-2. Perform test actions
-3. Verify assertions</t>
-  </si>
-  <si>
-    <t>Test executes successfully and all assertions pass</t>
+    <t>The user is logged in to OrangeHRM with valid credentials and the Dashboard has loaded. The user has navigated to the 'My Info' module.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Update the Personal Details form fields and save
+2. Reload the current page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The First Name field should not have the value ''
+- The nickname value should equal 'updatedNickname'
+- The other id value should equal 'randomOtherId'</t>
   </si>
   <si>
     <t>High</t>
@@ -81,155 +82,269 @@
     <t>Upload profile image</t>
   </si>
   <si>
+    <t>1. Upload a new profile image file</t>
+  </si>
+  <si>
+    <t>- The profile image container should be visible</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_03</t>
+  </si>
+  <si>
+    <t>Verify first name field is pre-populated</t>
+  </si>
+  <si>
+    <t>1. Perform the actions described in the test title</t>
+  </si>
+  <si>
+    <t>- The length should be greater than '0'</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_04</t>
+  </si>
+  <si>
+    <t>Verify My Info page heading displays Personal Details</t>
+  </si>
+  <si>
+    <t>- The orangehrm main title element should display the text 'Personal Details'</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_05</t>
+  </si>
+  <si>
+    <t>Verify Contact Details sub-tab is visible</t>
+  </si>
+  <si>
+    <t>- The 'Contact Details' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_06</t>
+  </si>
+  <si>
+    <t>Verify Emergency Contacts sub-tab is visible</t>
+  </si>
+  <si>
+    <t>- The 'Emergency Contacts' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_07</t>
+  </si>
+  <si>
+    <t>Verify Dependents sub-tab is visible</t>
+  </si>
+  <si>
+    <t>- The 'Dependents' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_08</t>
+  </si>
+  <si>
+    <t>Verify Immigration sub-tab is visible</t>
+  </si>
+  <si>
+    <t>- The 'Immigration' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_09</t>
+  </si>
+  <si>
+    <t>Verify Job sub-tab is visible</t>
+  </si>
+  <si>
+    <t>- The 'Job' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_10</t>
+  </si>
+  <si>
+    <t>Verify Salary sub-tab is visible</t>
+  </si>
+  <si>
+    <t>- The 'Salary' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_11</t>
+  </si>
+  <si>
+    <t>Verify Tax Exemptions sub-tab is visible</t>
+  </si>
+  <si>
+    <t>- The 'Tax Exemptions' element should be visible</t>
+  </si>
+  <si>
     <t>FAILED</t>
   </si>
   <si>
-    <t>TC_MYINFO_03</t>
-  </si>
-  <si>
-    <t>Verify first name field is pre-populated</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_04</t>
-  </si>
-  <si>
-    <t>Verify My Info page heading displays Personal Details</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_05</t>
-  </si>
-  <si>
-    <t>Verify Contact Details sub-tab is visible</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_06</t>
-  </si>
-  <si>
-    <t>Verify Emergency Contacts sub-tab is visible</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_07</t>
-  </si>
-  <si>
-    <t>Verify Dependents sub-tab is visible</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_08</t>
-  </si>
-  <si>
-    <t>Verify Immigration sub-tab is visible</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_09</t>
-  </si>
-  <si>
-    <t>Verify Job sub-tab is visible</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_10</t>
-  </si>
-  <si>
-    <t>Verify Salary sub-tab is visible</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_11</t>
-  </si>
-  <si>
-    <t>Verify Tax Exemptions sub-tab is visible</t>
-  </si>
-  <si>
     <t>TC_MYINFO_12</t>
   </si>
   <si>
     <t>Verify Report-to sub-tab is visible</t>
   </si>
   <si>
+    <t>- The 'Report-to' element should be visible</t>
+  </si>
+  <si>
     <t>TC_MYINFO_13</t>
   </si>
   <si>
     <t>Verify Qualifications sub-tab is visible</t>
   </si>
   <si>
+    <t>- The 'Qualifications' element should be visible</t>
+  </si>
+  <si>
     <t>TC_MYINFO_14</t>
   </si>
   <si>
     <t>Verify Memberships sub-tab is visible</t>
   </si>
   <si>
+    <t>- The 'Memberships' element should be visible</t>
+  </si>
+  <si>
     <t>TC_MYINFO_15</t>
   </si>
   <si>
     <t>Verify middle name field is visible</t>
   </si>
   <si>
+    <t>- The middle name field should be visible</t>
+  </si>
+  <si>
     <t>TC_MYINFO_16</t>
   </si>
   <si>
     <t>Verify last name field is visible</t>
   </si>
   <si>
+    <t>- The last name field should be visible</t>
+  </si>
+  <si>
     <t>TC_MYINFO_17</t>
   </si>
   <si>
     <t>Verify Employee ID field is visible</t>
   </si>
   <si>
+    <t>- The 'Employee Id' element should be visible</t>
+  </si>
+  <si>
     <t>TC_MYINFO_18</t>
   </si>
   <si>
     <t>Verify Driver's License Number field is visible</t>
   </si>
   <si>
+    <t>- The Number element should be visible</t>
+  </si>
+  <si>
     <t>TC_MYINFO_19</t>
   </si>
   <si>
     <t>Verify SSN Number field is visible</t>
   </si>
   <si>
+    <t>- The 'SSN Number' element should be present</t>
+  </si>
+  <si>
     <t>TC_MYINFO_20</t>
   </si>
   <si>
     <t>Verify SIN Number field is visible</t>
   </si>
   <si>
+    <t>- The 'SIN Number' element should be present</t>
+  </si>
+  <si>
     <t>TC_MYINFO_21</t>
   </si>
   <si>
     <t>Verify Nationality dropdown is visible</t>
   </si>
   <si>
+    <t>- The 'Nationality' element should be visible</t>
+  </si>
+  <si>
     <t>TC_MYINFO_22</t>
   </si>
   <si>
     <t>Verify Marital Status dropdown is visible</t>
   </si>
   <si>
+    <t>- The 'Marital Status' element should be visible</t>
+  </si>
+  <si>
     <t>TC_MYINFO_23</t>
   </si>
   <si>
     <t>Verify Gender radio buttons exist</t>
   </si>
   <si>
+    <t xml:space="preserve">- The 'Female' element should be present
+- The 'Male' element should be present</t>
+  </si>
+  <si>
     <t>TC_MYINFO_24</t>
   </si>
   <si>
     <t>Verify Custom Fields heading is visible</t>
   </si>
   <si>
+    <t>- The 'Custom Fields' element should be present</t>
+  </si>
+  <si>
     <t>TC_MYINFO_25</t>
   </si>
   <si>
     <t>Verify Attachments Add button is visible</t>
+  </si>
+  <si>
+    <t>- The 'Add' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_26</t>
+  </si>
+  <si>
+    <t>Verify My Info page URL points to Personal Details view by default</t>
+  </si>
+  <si>
+    <t>- The page.url() should contain 'viewPersonalDetails'</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_27</t>
+  </si>
+  <si>
+    <t>Verify an overly long nickname value is accepted without crashing the Personal Details form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click the Save button
+2. Reload the current page</t>
+  </si>
+  <si>
+    <t>- The First Name field should not have the value ''</t>
+  </si>
+  <si>
+    <t>SKIPPED</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_28</t>
+  </si>
+  <si>
+    <t>Verify Employee Id field displays a non-empty value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The 'Employee Id' element should be visible
+- The length should be greater than '0'</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -259,8 +374,14 @@
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF5A6268"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -280,6 +401,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E3E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -321,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -333,6 +459,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -674,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -780,21 +909,21 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>22</v>
+      <c r="K3" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -803,22 +932,22 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -829,7 +958,7 @@
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -838,25 +967,25 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>19</v>
@@ -864,7 +993,7 @@
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -873,25 +1002,25 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>19</v>
@@ -899,7 +1028,7 @@
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -908,25 +1037,25 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>19</v>
@@ -934,7 +1063,7 @@
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -943,25 +1072,25 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>19</v>
@@ -969,7 +1098,7 @@
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -978,25 +1107,25 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>19</v>
@@ -1004,7 +1133,7 @@
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -1013,25 +1142,25 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>19</v>
@@ -1039,7 +1168,7 @@
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1048,25 +1177,25 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>19</v>
@@ -1074,7 +1203,7 @@
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1083,33 +1212,33 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1118,25 +1247,25 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>19</v>
@@ -1144,7 +1273,7 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1153,25 +1282,25 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>19</v>
@@ -1179,7 +1308,7 @@
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1188,25 +1317,25 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>19</v>
@@ -1214,7 +1343,7 @@
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1223,25 +1352,25 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>19</v>
@@ -1249,7 +1378,7 @@
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1258,25 +1387,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>19</v>
@@ -1284,7 +1413,7 @@
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1293,25 +1422,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>19</v>
@@ -1319,7 +1448,7 @@
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1328,33 +1457,33 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1363,25 +1492,25 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>19</v>
@@ -1389,7 +1518,7 @@
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1398,25 +1527,25 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>19</v>
@@ -1424,7 +1553,7 @@
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1433,25 +1562,25 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>19</v>
@@ -1459,7 +1588,7 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1468,25 +1597,25 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>19</v>
@@ -1494,7 +1623,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1503,25 +1632,25 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>19</v>
@@ -1529,7 +1658,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1538,25 +1667,25 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>19</v>
@@ -1564,7 +1693,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1573,27 +1702,132 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K26" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>19</v>
       </c>
     </row>

--- a/Results/TestCases/XLSX/myinfo_TestCases.xlsx
+++ b/Results/TestCases/XLSX/myinfo_TestCases.xlsx
@@ -175,70 +175,73 @@
     <t>- The 'Tax Exemptions' element should be visible</t>
   </si>
   <si>
+    <t>SKIPPED</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_12</t>
+  </si>
+  <si>
+    <t>Verify Report-to sub-tab is visible</t>
+  </si>
+  <si>
+    <t>- The 'Report-to' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_13</t>
+  </si>
+  <si>
+    <t>Verify Qualifications sub-tab is visible</t>
+  </si>
+  <si>
+    <t>- The 'Qualifications' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_14</t>
+  </si>
+  <si>
+    <t>Verify Memberships sub-tab is visible</t>
+  </si>
+  <si>
+    <t>- The 'Memberships' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_15</t>
+  </si>
+  <si>
+    <t>Verify middle name field is visible</t>
+  </si>
+  <si>
+    <t>- The middle name field should be visible</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_16</t>
+  </si>
+  <si>
+    <t>Verify last name field is visible</t>
+  </si>
+  <si>
+    <t>- The last name field should be visible</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_17</t>
+  </si>
+  <si>
+    <t>Verify Employee ID field is visible</t>
+  </si>
+  <si>
+    <t>- The 'Employee Id' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_MYINFO_18</t>
+  </si>
+  <si>
+    <t>Verify Driver's License Number field is visible</t>
+  </si>
+  <si>
+    <t>- The Number element should be visible</t>
+  </si>
+  <si>
     <t>FAILED</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_12</t>
-  </si>
-  <si>
-    <t>Verify Report-to sub-tab is visible</t>
-  </si>
-  <si>
-    <t>- The 'Report-to' element should be visible</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_13</t>
-  </si>
-  <si>
-    <t>Verify Qualifications sub-tab is visible</t>
-  </si>
-  <si>
-    <t>- The 'Qualifications' element should be visible</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_14</t>
-  </si>
-  <si>
-    <t>Verify Memberships sub-tab is visible</t>
-  </si>
-  <si>
-    <t>- The 'Memberships' element should be visible</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_15</t>
-  </si>
-  <si>
-    <t>Verify middle name field is visible</t>
-  </si>
-  <si>
-    <t>- The middle name field should be visible</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_16</t>
-  </si>
-  <si>
-    <t>Verify last name field is visible</t>
-  </si>
-  <si>
-    <t>- The last name field should be visible</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_17</t>
-  </si>
-  <si>
-    <t>Verify Employee ID field is visible</t>
-  </si>
-  <si>
-    <t>- The 'Employee Id' element should be visible</t>
-  </si>
-  <si>
-    <t>TC_MYINFO_18</t>
-  </si>
-  <si>
-    <t>Verify Driver's License Number field is visible</t>
-  </si>
-  <si>
-    <t>- The Number element should be visible</t>
   </si>
   <si>
     <t>TC_MYINFO_19</t>
@@ -325,9 +328,6 @@
   </si>
   <si>
     <t>- The First Name field should not have the value ''</t>
-  </si>
-  <si>
-    <t>SKIPPED</t>
   </si>
   <si>
     <t>TC_MYINFO_28</t>
@@ -370,13 +370,13 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFA51D24"/>
+      <color rgb="FF5A6268"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF5A6268"/>
+      <color rgb="FFA51D24"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
@@ -400,12 +400,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
+        <fgColor rgb="FFE2E3E5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E3E5"/>
+        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -1477,13 +1477,13 @@
       <c r="J19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>19</v>
+      <c r="K19" s="5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1492,13 +1492,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -1507,7 +1507,7 @@
         <v>26</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>31</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1527,13 +1527,13 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1542,7 +1542,7 @@
         <v>26</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>31</v>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1562,13 +1562,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1577,7 +1577,7 @@
         <v>26</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>31</v>
@@ -1588,7 +1588,7 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1597,13 +1597,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1612,7 +1612,7 @@
         <v>26</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>31</v>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1632,13 +1632,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1647,7 +1647,7 @@
         <v>26</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>31</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1667,13 +1667,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1682,7 +1682,7 @@
         <v>26</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>31</v>
@@ -1693,7 +1693,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1702,13 +1702,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1717,7 +1717,7 @@
         <v>26</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>31</v>
@@ -1728,7 +1728,7 @@
     </row>
     <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
@@ -1737,13 +1737,13 @@
         <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -1752,7 +1752,7 @@
         <v>26</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>31</v>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
@@ -1772,28 +1772,28 @@
         <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K28" s="5" t="s">
-        <v>103</v>
+      <c r="K28" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="29" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
